--- a/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\GDPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\GDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987BE93E-100E-4459-954D-E6D34231C48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="90" windowWidth="22995" windowHeight="11055"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="GDPbES" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -124,7 +138,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -189,9 +203,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -229,9 +243,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -266,7 +280,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -301,7 +315,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -474,7 +488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -565,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -842,147 +856,147 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:R14" si="1">$B3</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="T3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="U3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="X3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Y3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AA3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AB3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AC3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AF3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AG3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AI3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AK3">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.25">
@@ -990,147 +1004,147 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK4">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.25">
@@ -1138,147 +1152,147 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
@@ -1286,147 +1300,147 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK6">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.25">
@@ -1434,147 +1448,147 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.25">
@@ -1582,147 +1596,147 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK8">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.25">
@@ -1730,147 +1744,147 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI9">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
         <f t="shared" ref="D9:AK14" si="2">$B9</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK9">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.25">
@@ -1878,147 +1892,147 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="X10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Y10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AG10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AH10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK10">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
@@ -2618,7 +2632,6 @@
         <v>29</v>
       </c>
       <c r="B15">
-        <f>B11</f>
         <v>0</v>
       </c>
       <c r="C15">
@@ -2767,7 +2780,6 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <f>B11</f>
         <v>0</v>
       </c>
       <c r="C16">
@@ -2916,148 +2928,147 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <f>B9</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:AK17" si="5">C9</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK17">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
+++ b/InputData/elec/GDPbES/Guaranteed Dispatch Perc by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/GDPbES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\GDPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1401B4F-AEE0-9C45-83CB-0D16DBCE5A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05343278-D919-4054-85F8-3C5252B2550B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37815" yWindow="3960" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Notes:</t>
   </si>
@@ -87,9 +87,6 @@
     <t>natural gas peaker</t>
   </si>
   <si>
-    <t>natural gas nonpeaker</t>
-  </si>
-  <si>
     <t>GDPbES Guaranteed Dispatch Percentage by Electricity Source</t>
   </si>
   <si>
@@ -133,6 +130,33 @@
   </si>
   <si>
     <t>Guaranteed Dispatch Fraction (dimensionless)</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
   </si>
 </sst>
 </file>
@@ -491,86 +515,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -584,16 +608,16 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:BE17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BE25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="1" max="1" width="23.1796875" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:57" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1" s="2">
         <v>2015</v>
@@ -764,9 +788,9 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4">
         <v>0</v>
@@ -992,9 +1016,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B3" s="4">
         <v>0</v>
@@ -1220,9 +1244,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B4" s="4">
         <v>0</v>
@@ -1448,9 +1472,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4">
         <v>0</v>
@@ -1676,9 +1700,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4">
         <v>0</v>
@@ -1904,9 +1928,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4">
         <v>0</v>
@@ -2132,9 +2156,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
@@ -2360,9 +2384,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -2588,9 +2612,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4">
         <v>0</v>
@@ -2816,9 +2840,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <v>0</v>
@@ -3044,9 +3068,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <v>0</v>
@@ -3272,9 +3296,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <v>0</v>
@@ -3500,9 +3524,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B14" s="4">
         <v>0</v>
@@ -3728,9 +3752,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B15" s="4">
         <v>0</v>
@@ -3956,9 +3980,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B16" s="4">
         <v>0</v>
@@ -4184,9 +4208,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B17" s="4">
         <v>0</v>
@@ -4409,6 +4433,1830 @@
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4">
+        <f t="shared" ref="C18:BE18" si="11">C10</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AL18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AM18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AO18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AP18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AR18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AS18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AT18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AU18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AV18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AW18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AX18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AY18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BA18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BB18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BC18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BD18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BE18" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4">
+        <f t="shared" ref="C19:BE19" si="12">C11</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AK19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AO19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AP19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AR19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AS19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AT19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AU19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AV19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AW19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AX19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AY19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BA19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BB19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BC19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BD19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BE19" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="4">
+        <v>3</v>
+      </c>
+      <c r="C20" s="4">
+        <f t="shared" ref="C20:BE20" si="13">C12</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AE20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AG20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AH20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AI20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AK20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AO20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AP20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AR20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AS20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AT20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AU20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AV20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AW20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AX20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AY20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BA20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BB20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BC20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BD20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BE20" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="4">
+        <v>4</v>
+      </c>
+      <c r="C21" s="4">
+        <f t="shared" ref="C21:BE21" si="14">C13</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AB21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AE21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AG21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AH21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AI21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AK21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AL21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AM21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AO21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AP21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AR21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AS21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AT21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AU21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AV21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AW21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AX21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BA21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BB21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BC21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BD21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BE21" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="4">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4">
+        <f t="shared" ref="C22:BE22" si="15">C14</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AB22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AK22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AL22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AM22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AN22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AO22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AP22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AR22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AS22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AT22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AU22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AV22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AW22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AX22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AY22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="BA22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="BB22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="BC22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="BD22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="BE22" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="4">
+        <v>6</v>
+      </c>
+      <c r="C23" s="4">
+        <f t="shared" ref="C23:BE23" si="16">C15</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AH23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AI23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AK23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AL23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AM23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AN23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AO23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AP23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AR23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AS23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AT23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AU23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AV23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AW23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AX23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AY23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BA23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BB23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BC23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BD23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="BE23" s="4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="4">
+        <v>7</v>
+      </c>
+      <c r="C24" s="4">
+        <f t="shared" ref="C24:BE24" si="17">C16</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AH24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AI24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AK24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AL24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AM24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AN24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AO24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AP24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AR24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AS24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AT24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AU24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AV24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AW24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AX24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AY24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AZ24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BA24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BB24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BC24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BD24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BE24" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:57" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="4">
+        <v>8</v>
+      </c>
+      <c r="C25" s="4">
+        <f t="shared" ref="C25:BE25" si="18">C17</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AI25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AK25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AL25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AM25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AO25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AP25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AR25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AS25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AT25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AU25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AV25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AW25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AX25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AZ25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BA25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BC25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BD25" s="4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BE25" s="4">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
